--- a/artfynd/A 66637-2021 artfynd.xlsx
+++ b/artfynd/A 66637-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 66637-2021 artfynd.xlsx
+++ b/artfynd/A 66637-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2022,113 +2022,6 @@
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>112606925</v>
-      </c>
-      <c r="B14" t="n">
-        <v>91032</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Gammalsätern, Dlr</t>
-        </is>
-      </c>
-      <c r="Q14" t="n">
-        <v>411706</v>
-      </c>
-      <c r="R14" t="n">
-        <v>6831929</v>
-      </c>
-      <c r="S14" t="n">
-        <v>10</v>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>Älvdalen</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>Särna</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>2022-09-14</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>2022-09-14</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT14" t="inlineStr"/>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 66637-2021 artfynd.xlsx
+++ b/artfynd/A 66637-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7133612</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7133613</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7133830</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7134130</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7133592</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1259,6 +1289,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606925</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1356,6 +1391,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7134080</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1453,6 +1493,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7133834</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1550,6 +1595,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7133698</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1647,6 +1697,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7134067</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1744,6 +1799,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7134068</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1841,8 +1901,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7133675</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>